--- a/src/test/resources/campaigndetails.xlsx
+++ b/src/test/resources/campaigndetails.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270" activeTab="1"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="details" sheetId="1" r:id="rId1"/>
     <sheet name="Campaigns" sheetId="2" r:id="rId2"/>
+    <sheet name="recruiterlist" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="27">
   <si>
     <t xml:space="preserve">Startdate </t>
   </si>
@@ -91,6 +92,21 @@
   </si>
   <si>
     <t>Info admin (admin)</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Application Received</t>
+  </si>
+  <si>
+    <t>Joined</t>
+  </si>
+  <si>
+    <t>Arya A</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -513,50 +529,87 @@
     <col min="7" max="7" customWidth="true" width="14.0"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="18.85546875"/>
+    <col min="2" max="2" customWidth="true" width="27.28515625"/>
+    <col min="3" max="3" customWidth="true" width="31.28515625"/>
+  </cols>
+  <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
